--- a/SuppXLS/Scen_z_MACC-SRV-CAP-WEM.xlsx
+++ b/SuppXLS/Scen_z_MACC-SRV-CAP-WEM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F918DF6B-E238-49E1-B31D-009BD4A661C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0AF92C-8C41-4396-BDC4-52320D3274F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="103">
   <si>
     <t>Sum of Pv</t>
   </si>
@@ -251,15 +251,9 @@
     <t>SRVAHT</t>
   </si>
   <si>
-    <t>S-SH-*_HET_N1</t>
-  </si>
-  <si>
     <t>FX</t>
   </si>
   <si>
-    <t>WEM</t>
-  </si>
-  <si>
     <t>Units</t>
   </si>
   <si>
@@ -330,21 +324,45 @@
   </si>
   <si>
     <t>District Heating (Commercial)</t>
+  </si>
+  <si>
+    <t>WAM NEP25</t>
+  </si>
+  <si>
+    <t>For projected years we have provided here the number of dwellings that undertake energy efficiency measures that bring the dwelling from a BER worse than B2 to one of B2 or better, excluding solar PV. This may not align exactly with the wording of the CAP target  of "B2 cost optimal or carbon equivalent". For 2024 we include an estimate of the cumulative number of dwellings that have undergone upgrade works  from 2018-2024 that improved their BER rating to B2 or better through SEAI schemes or Local Authority schemes, excluding solar PV only upgrades.</t>
+  </si>
+  <si>
+    <t>Assume that this item is for HP retrofits, excluding HP installed in new dwellings. The figure given for 2024 is the total number of HPs installed through SEAI and Local Authority retrofit schemes for 2019-2024.</t>
+  </si>
+  <si>
+    <t>Assume includes public services</t>
+  </si>
+  <si>
+    <t>SRVHET</t>
+  </si>
+  <si>
+    <t>FT-SRVHET</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -753,12 +771,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -769,8 +781,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -928,21 +946,58 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
       </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -951,132 +1006,151 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color theme="1" tint="0.499984740745262"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="46">
+  <cellStyleXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="43" borderId="4" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="41"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="43" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0" xfId="41" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="41" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="41"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="43" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" xfId="41" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="41" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" xfId="41" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="0" xfId="41" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="41" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" xfId="41" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" xfId="41" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="41" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="41" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="41" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="45"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="45" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="41" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="41" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="41" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="46"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="46" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="12" xfId="46" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="46" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="46" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="42" borderId="0" xfId="45" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="45" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="45" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="46" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="13" xfId="46" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="41" borderId="13" xfId="46" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="42" borderId="13" xfId="46" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="46" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="46" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="45" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="40" borderId="12" xfId="45" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="12" xfId="45" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="42" borderId="12" xfId="45" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="42" borderId="12" xfId="45" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="43" borderId="12" xfId="45" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="45" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="46" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="16" xfId="46" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="46" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="0" xfId="45" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="45" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="46" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="46" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="40" borderId="19" xfId="46" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="46" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="40" borderId="13" xfId="46" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="13" xfId="46" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="40" borderId="12" xfId="46" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="46" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="45" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="46" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="45" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="41" borderId="15" xfId="45" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="42" borderId="15" xfId="45" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="41" borderId="12" xfId="45" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="12" xfId="45" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="12" xfId="45" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="1" fillId="42" borderId="12" xfId="45" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="1" fillId="41" borderId="12" xfId="45" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="42" borderId="12" xfId="45" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="40" borderId="12" xfId="46" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="40" borderId="13" xfId="46" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="41" borderId="12" xfId="46" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="46" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="46">
+  <cellStyles count="48">
     <cellStyle name="20% - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="22" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="26" builtinId="38" customBuiltin="1"/>
@@ -1117,12 +1191,14 @@
     <cellStyle name="Normal 10" xfId="42" xr:uid="{87145C91-2173-4BBC-A5BF-CBABA237CA17}"/>
     <cellStyle name="Normal 2" xfId="41" xr:uid="{6B4421A1-8F15-4E5B-A04E-A4DC65721E11}"/>
     <cellStyle name="Normal 3" xfId="45" xr:uid="{B7D24BDE-ADD5-4D84-986D-9FD7709FE064}"/>
+    <cellStyle name="Normal 4" xfId="46" xr:uid="{A32B3DE6-5A61-4FE8-8152-1A5CB4E9A15A}"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="43" xr:uid="{100800D8-EC1F-4C74-A177-951125BCCC6D}"/>
     <cellStyle name="Note 2" xfId="44" xr:uid="{400CBDC5-F4D7-4BD6-98FE-7098D08B57B3}"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="16" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Worksheet Title" xfId="47" xr:uid="{53158046-0323-4060-A325-53D78B61638D}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -5084,7 +5160,7 @@
         <v>71</v>
       </c>
       <c r="K57" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L57" s="9">
         <v>1</v>
@@ -5128,57 +5204,94 @@
         <v>CAP-SRV-DH</v>
       </c>
       <c r="E58" t="s">
+        <v>102</v>
+      </c>
+      <c r="H58" t="s">
+        <v>101</v>
+      </c>
+      <c r="K58" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="K58" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="L58" s="9">
+      <c r="L58" s="9"/>
+      <c r="M58" s="9">
         <v>1</v>
       </c>
-      <c r="M58" s="9"/>
       <c r="N58" s="9"/>
       <c r="O58" s="9">
         <v>5</v>
       </c>
       <c r="Q58" s="17">
         <f>M85*3.6</f>
-        <v>4.9500000000000013E-3</v>
+        <v>1.2959999999999998E-2</v>
       </c>
       <c r="R58" s="17">
-        <f>N85*3.6</f>
-        <v>4.9500000000000013E-3</v>
+        <f t="shared" ref="Q58:V58" si="8">N85*3.6</f>
+        <v>2.0160000000000001E-2</v>
       </c>
       <c r="S58" s="17">
-        <f>O85*3.6</f>
-        <v>4.9500000000000013E-3</v>
+        <f t="shared" si="8"/>
+        <v>2.0160000000000001E-2</v>
       </c>
       <c r="T58" s="17">
-        <f>P85*3.6</f>
-        <v>4.9499999999999987E-3</v>
+        <f t="shared" si="8"/>
+        <v>2.0160000000000001E-2</v>
       </c>
       <c r="U58" s="17">
-        <f>Q85*3.6</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>2.0160000000000001E-2</v>
       </c>
       <c r="V58" s="17">
-        <f>R85*3.6</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>0.22685759999999996</v>
       </c>
       <c r="W58" s="17">
-        <v>0</v>
-      </c>
-      <c r="X58" s="17"/>
-      <c r="Y58" s="17"/>
-      <c r="Z58" s="17"/>
-      <c r="AA58" s="17"/>
-      <c r="AB58" s="17"/>
-      <c r="AC58" s="17"/>
-      <c r="AD58" s="17"/>
-      <c r="AE58" s="17"/>
-      <c r="AF58" s="17"/>
-      <c r="AG58" s="17"/>
-      <c r="AH58" s="17"/>
+        <f t="shared" ref="W58" si="9">S85*3.6</f>
+        <v>0.43355519999999997</v>
+      </c>
+      <c r="X58" s="17">
+        <f t="shared" ref="X58" si="10">T85*3.6</f>
+        <v>0.64025280000000007</v>
+      </c>
+      <c r="Y58" s="17">
+        <f t="shared" ref="Y58" si="11">U85*3.6</f>
+        <v>1.3538275200000001</v>
+      </c>
+      <c r="Z58" s="17">
+        <f t="shared" ref="Z58" si="12">V85*3.6</f>
+        <v>2.0674022399999998</v>
+      </c>
+      <c r="AA58" s="17">
+        <f t="shared" ref="AA58" si="13">W85*3.6</f>
+        <v>2.7809769600000003</v>
+      </c>
+      <c r="AB58" s="17">
+        <f t="shared" ref="AB58" si="14">X85*3.6</f>
+        <v>3.4945516799999998</v>
+      </c>
+      <c r="AC58" s="17">
+        <f t="shared" ref="AC58" si="15">Y85*3.6</f>
+        <v>4.2081264000000003</v>
+      </c>
+      <c r="AD58" s="17">
+        <f t="shared" ref="AD58" si="16">Z85*3.6</f>
+        <v>4.9217011199999998</v>
+      </c>
+      <c r="AE58" s="17">
+        <f t="shared" ref="AE58" si="17">AA85*3.6</f>
+        <v>5.6352758400000003</v>
+      </c>
+      <c r="AF58" s="17">
+        <f t="shared" ref="AF58" si="18">AB85*3.6</f>
+        <v>6.3488505599999998</v>
+      </c>
+      <c r="AG58" s="17">
+        <f t="shared" ref="AG58" si="19">AC85*3.6</f>
+        <v>7.0624252800000002</v>
+      </c>
+      <c r="AH58" s="17">
+        <f t="shared" ref="AH58" si="20">AD85*3.6</f>
+        <v>7.7760000000000007</v>
+      </c>
       <c r="AI58" s="17"/>
       <c r="AJ58" s="17"/>
       <c r="AK58" s="17"/>
@@ -5194,12 +5307,13 @@
       <c r="N59" s="9"/>
       <c r="O59" s="9"/>
     </row>
-    <row r="68" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F68" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="G68" s="38" t="s">
-        <v>75</v>
+    <row r="68" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E68" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="F68" s="38"/>
+      <c r="G68" s="36" t="s">
+        <v>73</v>
       </c>
       <c r="H68" s="22">
         <v>2018</v>
@@ -5222,7 +5336,7 @@
       <c r="N68" s="22">
         <v>2024</v>
       </c>
-      <c r="O68" s="39">
+      <c r="O68" s="37">
         <v>2025</v>
       </c>
       <c r="P68" s="22">
@@ -5237,249 +5351,683 @@
       <c r="S68" s="22">
         <v>2029</v>
       </c>
-      <c r="T68" s="39">
+      <c r="T68" s="37">
         <v>2030</v>
       </c>
       <c r="U68" s="22">
         <v>2031</v>
       </c>
-    </row>
-    <row r="69" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F69" s="24" t="s">
+      <c r="V68" s="22">
+        <v>2032</v>
+      </c>
+      <c r="W68" s="22">
+        <v>2033</v>
+      </c>
+      <c r="X68" s="22">
+        <v>2034</v>
+      </c>
+      <c r="Y68" s="22">
+        <v>2035</v>
+      </c>
+      <c r="Z68" s="22">
+        <v>2036</v>
+      </c>
+      <c r="AA68" s="22">
+        <v>2037</v>
+      </c>
+      <c r="AB68" s="22">
+        <v>2038</v>
+      </c>
+      <c r="AC68" s="22">
+        <v>2039</v>
+      </c>
+      <c r="AD68" s="37">
+        <v>2040</v>
+      </c>
+      <c r="AE68" s="22">
+        <v>2041</v>
+      </c>
+      <c r="AF68" s="22">
+        <v>2042</v>
+      </c>
+      <c r="AG68" s="22">
+        <v>2043</v>
+      </c>
+      <c r="AH68" s="22">
+        <v>2044</v>
+      </c>
+      <c r="AI68" s="22">
+        <v>2045</v>
+      </c>
+      <c r="AJ68" s="22">
+        <v>2046</v>
+      </c>
+      <c r="AK68" s="22">
+        <v>2047</v>
+      </c>
+      <c r="AL68" s="22">
+        <v>2048</v>
+      </c>
+      <c r="AM68" s="22">
+        <v>2049</v>
+      </c>
+      <c r="AN68" s="37">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="69" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E69" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F69" s="24"/>
+      <c r="G69" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H69" s="39">
+        <v>4528</v>
+      </c>
+      <c r="I69" s="39">
+        <v>8473</v>
+      </c>
+      <c r="J69" s="39">
+        <v>12576</v>
+      </c>
+      <c r="K69" s="39">
+        <v>21085</v>
+      </c>
+      <c r="L69" s="39">
+        <v>36002</v>
+      </c>
+      <c r="M69" s="39">
+        <v>57730</v>
+      </c>
+      <c r="N69" s="39">
+        <v>76458.133004706353</v>
+      </c>
+      <c r="O69" s="39">
+        <v>101504.59834396423</v>
+      </c>
+      <c r="P69" s="39">
+        <v>131806.53391912146</v>
+      </c>
+      <c r="Q69" s="39">
+        <v>168374.62820670515</v>
+      </c>
+      <c r="R69" s="39">
+        <v>212769.94018992549</v>
+      </c>
+      <c r="S69" s="39">
+        <v>266253.76204901852</v>
+      </c>
+      <c r="T69" s="39">
+        <v>330739.76204901852</v>
+      </c>
+      <c r="U69" s="39">
+        <v>402894.63103844196</v>
+      </c>
+      <c r="V69" s="39">
+        <v>483270.38586238777</v>
+      </c>
+      <c r="W69" s="39">
+        <v>572769.39329977881</v>
+      </c>
+      <c r="X69" s="39">
+        <v>671364.76917221397</v>
+      </c>
+      <c r="Y69" s="39">
+        <v>803011.76917221397</v>
+      </c>
+      <c r="Z69" s="39">
+        <v>934123.03147115838</v>
+      </c>
+      <c r="AA69" s="39">
+        <v>1062667.5992603253</v>
+      </c>
+      <c r="AB69" s="39">
+        <v>1188757.2164680006</v>
+      </c>
+      <c r="AC69" s="39">
+        <v>1327958.622256465</v>
+      </c>
+      <c r="AD69" s="39">
+        <v>1470126.1569172072</v>
+      </c>
+      <c r="AE69" s="24"/>
+      <c r="AF69" s="24"/>
+      <c r="AG69" s="24"/>
+      <c r="AH69" s="24"/>
+      <c r="AI69" s="24"/>
+      <c r="AJ69" s="24"/>
+      <c r="AK69" s="24"/>
+      <c r="AL69" s="24"/>
+      <c r="AM69" s="24"/>
+      <c r="AN69" s="25"/>
+    </row>
+    <row r="70" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E70" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="G69" s="23" t="s">
+      <c r="F70" s="24"/>
+      <c r="G70" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H70" s="39">
+        <v>2791</v>
+      </c>
+      <c r="I70" s="39">
+        <v>6306</v>
+      </c>
+      <c r="J70" s="39">
+        <v>12228</v>
+      </c>
+      <c r="K70" s="39">
+        <v>23671</v>
+      </c>
+      <c r="L70" s="39">
+        <v>33157</v>
+      </c>
+      <c r="M70" s="39">
+        <v>46227</v>
+      </c>
+      <c r="N70" s="39">
+        <v>65580.100332647708</v>
+      </c>
+      <c r="O70" s="39">
+        <v>88429.861651536645</v>
+      </c>
+      <c r="P70" s="39">
+        <v>115259.45447616215</v>
+      </c>
+      <c r="Q70" s="39">
+        <v>146809.32931771784</v>
+      </c>
+      <c r="R70" s="39">
+        <v>183964.44466028124</v>
+      </c>
+      <c r="S70" s="39">
+        <v>227783.37094489671</v>
+      </c>
+      <c r="T70" s="39">
+        <v>279411.37094489671</v>
+      </c>
+      <c r="U70" s="39">
+        <v>332264.19836038561</v>
+      </c>
+      <c r="V70" s="39">
+        <v>387049.05666471604</v>
+      </c>
+      <c r="W70" s="39">
+        <v>443151.32676393108</v>
+      </c>
+      <c r="X70" s="39">
+        <v>501364.82754287875</v>
+      </c>
+      <c r="Y70" s="39">
+        <v>533242.82754287869</v>
+      </c>
+      <c r="Z70" s="39">
+        <v>553528.32832182629</v>
+      </c>
+      <c r="AA70" s="39">
+        <v>569779.54423927818</v>
+      </c>
+      <c r="AB70" s="39">
+        <v>578052.04909329861</v>
+      </c>
+      <c r="AC70" s="39">
+        <v>577462.83565678261</v>
+      </c>
+      <c r="AD70" s="39">
+        <v>570363.07433789363</v>
+      </c>
+      <c r="AE70" s="24"/>
+      <c r="AF70" s="24"/>
+      <c r="AG70" s="24"/>
+      <c r="AH70" s="24"/>
+      <c r="AI70" s="24"/>
+      <c r="AJ70" s="24"/>
+      <c r="AK70" s="24"/>
+      <c r="AL70" s="24"/>
+      <c r="AM70" s="24"/>
+      <c r="AN70" s="25"/>
+    </row>
+    <row r="71" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E71" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="H69" s="24"/>
-      <c r="I69" s="24"/>
-      <c r="J69" s="24"/>
-      <c r="K69" s="24"/>
-      <c r="L69" s="24"/>
-      <c r="M69" s="24"/>
-      <c r="N69" s="24"/>
-      <c r="O69" s="26"/>
-      <c r="P69" s="27">
-        <v>34399.399999999994</v>
-      </c>
-      <c r="Q69" s="27">
-        <v>34399.399999999994</v>
-      </c>
-      <c r="R69" s="27">
-        <v>34399.399999999994</v>
-      </c>
-      <c r="S69" s="27">
-        <v>34399.399999999994</v>
-      </c>
-      <c r="T69" s="26">
-        <v>34399.400000000023</v>
-      </c>
-      <c r="U69" s="24"/>
-    </row>
-    <row r="70" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F70" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="G70" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="H70" s="24"/>
-      <c r="I70" s="24"/>
-      <c r="J70" s="24"/>
-      <c r="K70" s="24"/>
-      <c r="L70" s="24"/>
-      <c r="M70" s="24"/>
-      <c r="N70" s="24"/>
-      <c r="O70" s="26"/>
-      <c r="P70" s="28">
-        <v>38196</v>
-      </c>
-      <c r="Q70" s="28">
-        <v>38196</v>
-      </c>
-      <c r="R70" s="28">
-        <v>38196</v>
-      </c>
-      <c r="S70" s="28">
-        <v>38196</v>
-      </c>
-      <c r="T70" s="26">
-        <v>38196</v>
-      </c>
-      <c r="U70" s="24"/>
-    </row>
-    <row r="71" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F71" s="24" t="s">
-        <v>79</v>
-      </c>
+      <c r="F71" s="20"/>
       <c r="G71" s="23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H71" s="24"/>
       <c r="I71" s="24"/>
       <c r="J71" s="24"/>
       <c r="K71" s="24"/>
       <c r="L71" s="24"/>
-      <c r="M71" s="29">
+      <c r="M71" s="27">
         <v>61</v>
       </c>
-      <c r="N71" s="29">
-        <v>221</v>
-      </c>
-      <c r="O71" s="28">
-        <v>0</v>
-      </c>
-      <c r="P71" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="28">
-        <v>0</v>
-      </c>
-      <c r="R71" s="28">
-        <v>0</v>
-      </c>
-      <c r="S71" s="28">
-        <v>0</v>
-      </c>
-      <c r="T71" s="28">
-        <v>0</v>
-      </c>
-      <c r="U71" s="24"/>
-    </row>
-    <row r="72" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F72" s="24" t="s">
+      <c r="N71" s="27">
+        <v>282</v>
+      </c>
+      <c r="O71" s="39">
+        <v>282</v>
+      </c>
+      <c r="P71" s="39">
+        <v>282</v>
+      </c>
+      <c r="Q71" s="39">
+        <v>282</v>
+      </c>
+      <c r="R71" s="39">
+        <v>282</v>
+      </c>
+      <c r="S71" s="39">
+        <v>282</v>
+      </c>
+      <c r="T71" s="39">
+        <v>282</v>
+      </c>
+      <c r="U71" s="39">
+        <v>282</v>
+      </c>
+      <c r="V71" s="39">
+        <v>282</v>
+      </c>
+      <c r="W71" s="39">
+        <v>282</v>
+      </c>
+      <c r="X71" s="39">
+        <v>282</v>
+      </c>
+      <c r="Y71" s="39">
+        <v>282</v>
+      </c>
+      <c r="Z71" s="39">
+        <v>282</v>
+      </c>
+      <c r="AA71" s="39">
+        <v>282</v>
+      </c>
+      <c r="AB71" s="39">
+        <v>282</v>
+      </c>
+      <c r="AC71" s="39">
+        <v>282</v>
+      </c>
+      <c r="AD71" s="39">
+        <v>282</v>
+      </c>
+      <c r="AE71" s="24"/>
+      <c r="AF71" s="24"/>
+      <c r="AG71" s="24"/>
+      <c r="AH71" s="24"/>
+      <c r="AI71" s="24"/>
+      <c r="AJ71" s="24"/>
+      <c r="AK71" s="24"/>
+      <c r="AL71" s="24"/>
+      <c r="AM71" s="24"/>
+      <c r="AN71" s="25"/>
+    </row>
+    <row r="72" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E72" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="F72" s="20"/>
+      <c r="G72" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H72" s="39">
+        <v>10</v>
+      </c>
+      <c r="I72" s="39">
+        <v>57</v>
+      </c>
+      <c r="J72" s="39">
+        <v>103</v>
+      </c>
+      <c r="K72" s="39">
+        <v>208</v>
+      </c>
+      <c r="L72" s="39">
+        <v>379</v>
+      </c>
+      <c r="M72" s="39">
+        <v>675</v>
+      </c>
+      <c r="N72" s="39">
+        <v>937.5</v>
+      </c>
+      <c r="O72" s="39">
+        <v>1200</v>
+      </c>
+      <c r="P72" s="39">
+        <v>2160</v>
+      </c>
+      <c r="Q72" s="39">
+        <v>3120</v>
+      </c>
+      <c r="R72" s="39">
+        <v>4080</v>
+      </c>
+      <c r="S72" s="39">
+        <v>5040</v>
+      </c>
+      <c r="T72" s="39">
+        <v>6000</v>
+      </c>
+      <c r="U72" s="39">
+        <v>7800</v>
+      </c>
+      <c r="V72" s="39">
+        <v>9600</v>
+      </c>
+      <c r="W72" s="39">
+        <v>11400</v>
+      </c>
+      <c r="X72" s="39">
+        <v>13200</v>
+      </c>
+      <c r="Y72" s="39">
+        <v>15000</v>
+      </c>
+      <c r="Z72" s="39">
+        <v>14000</v>
+      </c>
+      <c r="AA72" s="39">
+        <v>13000</v>
+      </c>
+      <c r="AB72" s="39">
+        <v>12000</v>
+      </c>
+      <c r="AC72" s="39">
+        <v>11000</v>
+      </c>
+      <c r="AD72" s="39">
+        <v>10000</v>
+      </c>
+      <c r="AE72" s="24"/>
+      <c r="AF72" s="24"/>
+      <c r="AG72" s="24"/>
+      <c r="AH72" s="24"/>
+      <c r="AI72" s="24"/>
+      <c r="AJ72" s="24"/>
+      <c r="AK72" s="24"/>
+      <c r="AL72" s="24"/>
+      <c r="AM72" s="24"/>
+      <c r="AN72" s="25"/>
+    </row>
+    <row r="73" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E73" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="F73" s="24"/>
+      <c r="G73" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H73" s="24">
+        <v>167</v>
+      </c>
+      <c r="I73" s="24">
+        <v>454</v>
+      </c>
+      <c r="J73" s="24">
+        <v>878</v>
+      </c>
+      <c r="K73" s="24">
+        <v>1770</v>
+      </c>
+      <c r="L73" s="24">
+        <v>2135</v>
+      </c>
+      <c r="M73" s="24">
+        <v>2856</v>
+      </c>
+      <c r="N73" s="24">
+        <v>3926.2142857142858</v>
+      </c>
+      <c r="O73" s="24">
+        <v>4996.4285714285716</v>
+      </c>
+      <c r="P73" s="24">
+        <v>8917.1428571428569</v>
+      </c>
+      <c r="Q73" s="24">
+        <v>12837.857142857143</v>
+      </c>
+      <c r="R73" s="24">
+        <v>16758.571428571428</v>
+      </c>
+      <c r="S73" s="24">
+        <v>20679.285714285714</v>
+      </c>
+      <c r="T73" s="24">
+        <v>24600</v>
+      </c>
+      <c r="U73" s="24">
+        <v>29090</v>
+      </c>
+      <c r="V73" s="24">
+        <v>33580</v>
+      </c>
+      <c r="W73" s="24">
+        <v>38070</v>
+      </c>
+      <c r="X73" s="24">
+        <v>42560</v>
+      </c>
+      <c r="Y73" s="24">
+        <v>47050</v>
+      </c>
+      <c r="Z73" s="24">
+        <v>69184.874566279919</v>
+      </c>
+      <c r="AA73" s="24">
+        <v>91319.749132559838</v>
+      </c>
+      <c r="AB73" s="24">
+        <v>113454.62369883976</v>
+      </c>
+      <c r="AC73" s="24">
+        <v>135589.49826511968</v>
+      </c>
+      <c r="AD73" s="24">
+        <v>157724.37283139961</v>
+      </c>
+      <c r="AE73" s="24"/>
+      <c r="AF73" s="24"/>
+      <c r="AG73" s="24"/>
+      <c r="AH73" s="24"/>
+      <c r="AI73" s="24"/>
+      <c r="AJ73" s="24"/>
+      <c r="AK73" s="24"/>
+      <c r="AL73" s="24"/>
+      <c r="AM73" s="24"/>
+      <c r="AN73" s="25"/>
+    </row>
+    <row r="74" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E74" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="G72" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="H72" s="24"/>
-      <c r="I72" s="24"/>
-      <c r="J72" s="24"/>
-      <c r="K72" s="24"/>
-      <c r="L72" s="24"/>
-      <c r="M72" s="24"/>
-      <c r="N72" s="24"/>
-      <c r="O72" s="26"/>
-      <c r="P72" s="28">
-        <v>660</v>
-      </c>
-      <c r="Q72" s="28">
-        <v>660</v>
-      </c>
-      <c r="R72" s="28">
-        <v>660</v>
-      </c>
-      <c r="S72" s="28">
-        <v>660</v>
-      </c>
-      <c r="T72" s="26">
-        <v>660</v>
-      </c>
-      <c r="U72" s="24"/>
-    </row>
-    <row r="73" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F73" s="24" t="s">
+      <c r="F74" s="40"/>
+      <c r="G74" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="H74" s="39">
+        <v>167</v>
+      </c>
+      <c r="I74" s="39">
+        <v>454</v>
+      </c>
+      <c r="J74" s="39">
+        <v>878</v>
+      </c>
+      <c r="K74" s="39">
+        <v>1770</v>
+      </c>
+      <c r="L74" s="39">
+        <v>2135</v>
+      </c>
+      <c r="M74" s="39">
+        <v>2821</v>
+      </c>
+      <c r="N74" s="39">
+        <v>3810.5</v>
+      </c>
+      <c r="O74" s="39">
+        <v>4800</v>
+      </c>
+      <c r="P74" s="39">
+        <v>8640</v>
+      </c>
+      <c r="Q74" s="39">
+        <v>12480</v>
+      </c>
+      <c r="R74" s="39">
+        <v>16320</v>
+      </c>
+      <c r="S74" s="39">
+        <v>20160</v>
+      </c>
+      <c r="T74" s="39">
+        <v>24000</v>
+      </c>
+      <c r="U74" s="39">
+        <v>28200</v>
+      </c>
+      <c r="V74" s="39">
+        <v>32400</v>
+      </c>
+      <c r="W74" s="39">
+        <v>36600</v>
+      </c>
+      <c r="X74" s="39">
+        <v>40800</v>
+      </c>
+      <c r="Y74" s="39">
+        <v>45000</v>
+      </c>
+      <c r="Z74" s="39">
+        <v>66844.874566279919</v>
+      </c>
+      <c r="AA74" s="39">
+        <v>88689.749132559838</v>
+      </c>
+      <c r="AB74" s="39">
+        <v>110534.62369883976</v>
+      </c>
+      <c r="AC74" s="39">
+        <v>132379.49826511968</v>
+      </c>
+      <c r="AD74" s="39">
+        <v>154224.37283139961</v>
+      </c>
+      <c r="AE74" s="30"/>
+      <c r="AF74" s="30"/>
+      <c r="AG74" s="30"/>
+      <c r="AH74" s="30"/>
+      <c r="AI74" s="30"/>
+      <c r="AJ74" s="30"/>
+      <c r="AK74" s="30"/>
+      <c r="AL74" s="30"/>
+      <c r="AM74" s="30"/>
+      <c r="AN74" s="31"/>
+    </row>
+    <row r="75" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E75" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="G73" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="H73" s="24"/>
-      <c r="I73" s="24"/>
-      <c r="J73" s="24"/>
-      <c r="K73" s="24"/>
-      <c r="L73" s="24"/>
-      <c r="M73" s="24"/>
-      <c r="N73" s="24"/>
-      <c r="O73" s="26"/>
-      <c r="P73" s="28">
-        <v>1168</v>
-      </c>
-      <c r="Q73" s="28">
-        <v>1168</v>
-      </c>
-      <c r="R73" s="28">
-        <v>1168</v>
-      </c>
-      <c r="S73" s="28">
-        <v>1168</v>
-      </c>
-      <c r="T73" s="26">
-        <v>1168</v>
-      </c>
-      <c r="U73" s="24"/>
-    </row>
-    <row r="74" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F74" s="30" t="s">
+      <c r="F75" s="41"/>
+      <c r="G75" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="H75" s="39">
+        <v>0</v>
+      </c>
+      <c r="I75" s="39">
+        <v>0</v>
+      </c>
+      <c r="J75" s="39">
+        <v>0</v>
+      </c>
+      <c r="K75" s="39">
+        <v>0</v>
+      </c>
+      <c r="L75" s="39">
+        <v>0</v>
+      </c>
+      <c r="M75" s="39">
+        <v>35</v>
+      </c>
+      <c r="N75" s="39">
+        <v>115.71428571428571</v>
+      </c>
+      <c r="O75" s="39">
+        <v>196.42857142857142</v>
+      </c>
+      <c r="P75" s="39">
+        <v>277.14285714285711</v>
+      </c>
+      <c r="Q75" s="39">
+        <v>357.85714285714283</v>
+      </c>
+      <c r="R75" s="39">
+        <v>438.57142857142856</v>
+      </c>
+      <c r="S75" s="39">
+        <v>519.28571428571422</v>
+      </c>
+      <c r="T75" s="39">
+        <v>600</v>
+      </c>
+      <c r="U75" s="39">
+        <v>890</v>
+      </c>
+      <c r="V75" s="39">
+        <v>1180</v>
+      </c>
+      <c r="W75" s="39">
+        <v>1470</v>
+      </c>
+      <c r="X75" s="39">
+        <v>1760</v>
+      </c>
+      <c r="Y75" s="39">
+        <v>2050</v>
+      </c>
+      <c r="Z75" s="39">
+        <v>2340</v>
+      </c>
+      <c r="AA75" s="39">
+        <v>2630</v>
+      </c>
+      <c r="AB75" s="39">
+        <v>2920</v>
+      </c>
+      <c r="AC75" s="39">
+        <v>3210</v>
+      </c>
+      <c r="AD75" s="39">
+        <v>3500</v>
+      </c>
+      <c r="AE75" s="34"/>
+      <c r="AF75" s="34"/>
+      <c r="AG75" s="34"/>
+      <c r="AH75" s="34"/>
+      <c r="AI75" s="34"/>
+      <c r="AJ75" s="34"/>
+      <c r="AK75" s="34"/>
+      <c r="AL75" s="34"/>
+      <c r="AM75" s="34"/>
+      <c r="AN75" s="35"/>
+    </row>
+    <row r="76" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E76" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="G74" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="H74" s="19"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="19"/>
-      <c r="K74" s="19"/>
-      <c r="L74" s="19"/>
-      <c r="M74" s="19"/>
-      <c r="N74" s="19"/>
-      <c r="O74" s="31"/>
-      <c r="P74" s="21">
-        <v>1140</v>
-      </c>
-      <c r="Q74" s="21">
-        <v>1140</v>
-      </c>
-      <c r="R74" s="21">
-        <v>1140</v>
-      </c>
-      <c r="S74" s="21">
-        <v>1140</v>
-      </c>
-      <c r="T74" s="31">
-        <v>1140</v>
-      </c>
-      <c r="U74" s="19"/>
-    </row>
-    <row r="75" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F75" s="32" t="s">
+      <c r="F76" s="24"/>
+      <c r="G76" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="G75" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="H75" s="34"/>
-      <c r="I75" s="34"/>
-      <c r="J75" s="34"/>
-      <c r="K75" s="34"/>
-      <c r="L75" s="34"/>
-      <c r="M75" s="34"/>
-      <c r="N75" s="34"/>
-      <c r="O75" s="35"/>
-      <c r="P75" s="36">
-        <v>28</v>
-      </c>
-      <c r="Q75" s="36">
-        <v>28</v>
-      </c>
-      <c r="R75" s="36">
-        <v>28</v>
-      </c>
-      <c r="S75" s="36">
-        <v>28</v>
-      </c>
-      <c r="T75" s="35">
-        <v>28</v>
-      </c>
-      <c r="U75" s="34"/>
-    </row>
-    <row r="76" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F76" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="G76" s="23" t="s">
-        <v>85</v>
       </c>
       <c r="H76" s="24"/>
       <c r="I76" s="24"/>
@@ -5487,35 +6035,75 @@
       <c r="K76" s="24"/>
       <c r="L76" s="24"/>
       <c r="M76" s="24"/>
-      <c r="N76" s="25"/>
-      <c r="O76" s="25">
-        <v>250</v>
-      </c>
-      <c r="P76" s="25">
-        <v>250</v>
-      </c>
-      <c r="Q76" s="25">
-        <v>250</v>
-      </c>
-      <c r="R76" s="25">
-        <v>250</v>
-      </c>
-      <c r="S76" s="25">
-        <v>250</v>
-      </c>
-      <c r="T76" s="25">
-        <v>250</v>
-      </c>
-      <c r="U76" s="25">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="77" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F77" s="24" t="s">
-        <v>86</v>
-      </c>
+      <c r="N76" s="39">
+        <v>4740.55</v>
+      </c>
+      <c r="O76" s="39">
+        <v>5044.28125</v>
+      </c>
+      <c r="P76" s="39">
+        <v>5540.25</v>
+      </c>
+      <c r="Q76" s="39">
+        <v>5865.5</v>
+      </c>
+      <c r="R76" s="39">
+        <v>6207.875</v>
+      </c>
+      <c r="S76" s="39">
+        <v>6579.75</v>
+      </c>
+      <c r="T76" s="39">
+        <v>6930.625</v>
+      </c>
+      <c r="U76" s="39">
+        <v>7281.125</v>
+      </c>
+      <c r="V76" s="39">
+        <v>7685.25</v>
+      </c>
+      <c r="W76" s="39">
+        <v>8093.125</v>
+      </c>
+      <c r="X76" s="39">
+        <v>8507.5</v>
+      </c>
+      <c r="Y76" s="39">
+        <v>8927.125</v>
+      </c>
+      <c r="Z76" s="39">
+        <v>9282</v>
+      </c>
+      <c r="AA76" s="39">
+        <v>9591.5</v>
+      </c>
+      <c r="AB76" s="39">
+        <v>9953.25</v>
+      </c>
+      <c r="AC76" s="39">
+        <v>10242.5</v>
+      </c>
+      <c r="AD76" s="39">
+        <v>10550.5</v>
+      </c>
+      <c r="AE76" s="24"/>
+      <c r="AF76" s="24"/>
+      <c r="AG76" s="24"/>
+      <c r="AH76" s="24"/>
+      <c r="AI76" s="24"/>
+      <c r="AJ76" s="24"/>
+      <c r="AK76" s="24"/>
+      <c r="AL76" s="24"/>
+      <c r="AM76" s="24"/>
+      <c r="AN76" s="25"/>
+    </row>
+    <row r="77" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E77" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="F77" s="24"/>
       <c r="G77" s="23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H77" s="24"/>
       <c r="I77" s="24"/>
@@ -5523,35 +6111,75 @@
       <c r="K77" s="24"/>
       <c r="L77" s="24"/>
       <c r="M77" s="24"/>
-      <c r="N77" s="25"/>
-      <c r="O77" s="25">
-        <v>0</v>
-      </c>
-      <c r="P77" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="25">
-        <v>0</v>
-      </c>
-      <c r="R77" s="25">
-        <v>0</v>
-      </c>
-      <c r="S77" s="25">
-        <v>825</v>
-      </c>
-      <c r="T77" s="25">
-        <v>1800</v>
-      </c>
-      <c r="U77" s="25">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="78" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F78" s="24" t="s">
-        <v>87</v>
-      </c>
+      <c r="N77" s="39">
+        <v>25</v>
+      </c>
+      <c r="O77" s="39">
+        <v>25</v>
+      </c>
+      <c r="P77" s="39">
+        <v>25</v>
+      </c>
+      <c r="Q77" s="39">
+        <v>25</v>
+      </c>
+      <c r="R77" s="39">
+        <v>25</v>
+      </c>
+      <c r="S77" s="39">
+        <v>231.25</v>
+      </c>
+      <c r="T77" s="39">
+        <v>1525</v>
+      </c>
+      <c r="U77" s="39">
+        <v>2862.5</v>
+      </c>
+      <c r="V77" s="39">
+        <v>3500</v>
+      </c>
+      <c r="W77" s="39">
+        <v>4000</v>
+      </c>
+      <c r="X77" s="39">
+        <v>4500</v>
+      </c>
+      <c r="Y77" s="39">
+        <v>5175</v>
+      </c>
+      <c r="Z77" s="39">
+        <v>5875</v>
+      </c>
+      <c r="AA77" s="39">
+        <v>6575</v>
+      </c>
+      <c r="AB77" s="39">
+        <v>7350</v>
+      </c>
+      <c r="AC77" s="39">
+        <v>8350</v>
+      </c>
+      <c r="AD77" s="39">
+        <v>9325</v>
+      </c>
+      <c r="AE77" s="24"/>
+      <c r="AF77" s="24"/>
+      <c r="AG77" s="24"/>
+      <c r="AH77" s="24"/>
+      <c r="AI77" s="24"/>
+      <c r="AJ77" s="24"/>
+      <c r="AK77" s="24"/>
+      <c r="AL77" s="24"/>
+      <c r="AM77" s="24"/>
+      <c r="AN77" s="25"/>
+    </row>
+    <row r="78" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E78" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F78" s="24"/>
       <c r="G78" s="23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H78" s="24"/>
       <c r="I78" s="24"/>
@@ -5559,35 +6187,75 @@
       <c r="K78" s="24"/>
       <c r="L78" s="24"/>
       <c r="M78" s="24"/>
-      <c r="N78" s="25"/>
-      <c r="O78" s="25">
-        <v>1011</v>
-      </c>
-      <c r="P78" s="25">
-        <v>373</v>
-      </c>
-      <c r="Q78" s="25">
-        <v>1020</v>
-      </c>
-      <c r="R78" s="25">
-        <v>535</v>
-      </c>
-      <c r="S78" s="25">
-        <v>785</v>
-      </c>
-      <c r="T78" s="25">
-        <v>836</v>
-      </c>
-      <c r="U78" s="25">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="79" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F79" s="24" t="s">
-        <v>88</v>
-      </c>
+      <c r="N78" s="39">
+        <v>914.93749999999989</v>
+      </c>
+      <c r="O78" s="39">
+        <v>1680.75</v>
+      </c>
+      <c r="P78" s="39">
+        <v>2789.75</v>
+      </c>
+      <c r="Q78" s="39">
+        <v>3543.375</v>
+      </c>
+      <c r="R78" s="39">
+        <v>4296.75</v>
+      </c>
+      <c r="S78" s="39">
+        <v>5050.375</v>
+      </c>
+      <c r="T78" s="39">
+        <v>5805.25</v>
+      </c>
+      <c r="U78" s="39">
+        <v>6505.5</v>
+      </c>
+      <c r="V78" s="39">
+        <v>7105.375</v>
+      </c>
+      <c r="W78" s="39">
+        <v>7695.375</v>
+      </c>
+      <c r="X78" s="39">
+        <v>8277.75</v>
+      </c>
+      <c r="Y78" s="39">
+        <v>8857.625</v>
+      </c>
+      <c r="Z78" s="39">
+        <v>9402.375</v>
+      </c>
+      <c r="AA78" s="39">
+        <v>9880</v>
+      </c>
+      <c r="AB78" s="39">
+        <v>10349.75</v>
+      </c>
+      <c r="AC78" s="39">
+        <v>10812.75</v>
+      </c>
+      <c r="AD78" s="39">
+        <v>11268.5</v>
+      </c>
+      <c r="AE78" s="24"/>
+      <c r="AF78" s="24"/>
+      <c r="AG78" s="24"/>
+      <c r="AH78" s="24"/>
+      <c r="AI78" s="24"/>
+      <c r="AJ78" s="24"/>
+      <c r="AK78" s="24"/>
+      <c r="AL78" s="24"/>
+      <c r="AM78" s="24"/>
+      <c r="AN78" s="25"/>
+    </row>
+    <row r="79" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E79" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F79" s="24"/>
       <c r="G79" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H79" s="24"/>
       <c r="I79" s="24"/>
@@ -5596,32 +6264,72 @@
       <c r="L79" s="24"/>
       <c r="M79" s="24"/>
       <c r="N79" s="24"/>
-      <c r="O79" s="26">
+      <c r="O79" s="39">
         <v>10</v>
       </c>
-      <c r="P79" s="28">
+      <c r="P79" s="26">
         <v>10</v>
       </c>
-      <c r="Q79" s="28">
+      <c r="Q79" s="26">
         <v>10</v>
       </c>
-      <c r="R79" s="28">
+      <c r="R79" s="26">
         <v>10</v>
       </c>
-      <c r="S79" s="28">
+      <c r="S79" s="26">
         <v>10</v>
       </c>
-      <c r="T79" s="26">
+      <c r="T79" s="39">
         <v>10</v>
       </c>
-      <c r="U79" s="24"/>
-    </row>
-    <row r="80" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F80" s="24" t="s">
-        <v>90</v>
-      </c>
+      <c r="U79" s="21">
+        <v>10</v>
+      </c>
+      <c r="V79" s="21">
+        <v>10</v>
+      </c>
+      <c r="W79" s="21">
+        <v>10</v>
+      </c>
+      <c r="X79" s="21">
+        <v>10</v>
+      </c>
+      <c r="Y79" s="21">
+        <v>10</v>
+      </c>
+      <c r="Z79" s="21">
+        <v>10</v>
+      </c>
+      <c r="AA79" s="21">
+        <v>10</v>
+      </c>
+      <c r="AB79" s="21">
+        <v>10</v>
+      </c>
+      <c r="AC79" s="21">
+        <v>10</v>
+      </c>
+      <c r="AD79" s="21">
+        <v>10</v>
+      </c>
+      <c r="AE79" s="24"/>
+      <c r="AF79" s="24"/>
+      <c r="AG79" s="24"/>
+      <c r="AH79" s="24"/>
+      <c r="AI79" s="24"/>
+      <c r="AJ79" s="24"/>
+      <c r="AK79" s="24"/>
+      <c r="AL79" s="24"/>
+      <c r="AM79" s="24"/>
+      <c r="AN79" s="25"/>
+    </row>
+    <row r="80" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E80" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="F80" s="24"/>
       <c r="G80" s="23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H80" s="24"/>
       <c r="I80" s="24"/>
@@ -5630,32 +6338,72 @@
       <c r="L80" s="24"/>
       <c r="M80" s="24"/>
       <c r="N80" s="24"/>
-      <c r="O80" s="26">
+      <c r="O80" s="39">
         <v>12</v>
       </c>
-      <c r="P80" s="28">
+      <c r="P80" s="26">
         <v>13.6</v>
       </c>
-      <c r="Q80" s="28">
+      <c r="Q80" s="26">
         <v>15.2</v>
       </c>
-      <c r="R80" s="28">
+      <c r="R80" s="26">
         <v>16.8</v>
       </c>
-      <c r="S80" s="28">
+      <c r="S80" s="26">
         <v>18.400000000000002</v>
       </c>
-      <c r="T80" s="26">
+      <c r="T80" s="39">
         <v>20</v>
       </c>
-      <c r="U80" s="24"/>
-    </row>
-    <row r="81" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F81" s="24" t="s">
-        <v>91</v>
-      </c>
+      <c r="U80" s="21">
+        <v>20</v>
+      </c>
+      <c r="V80" s="21">
+        <v>20</v>
+      </c>
+      <c r="W80" s="21">
+        <v>20</v>
+      </c>
+      <c r="X80" s="21">
+        <v>20</v>
+      </c>
+      <c r="Y80" s="21">
+        <v>20</v>
+      </c>
+      <c r="Z80" s="21">
+        <v>20</v>
+      </c>
+      <c r="AA80" s="21">
+        <v>20</v>
+      </c>
+      <c r="AB80" s="21">
+        <v>20</v>
+      </c>
+      <c r="AC80" s="21">
+        <v>20</v>
+      </c>
+      <c r="AD80" s="21">
+        <v>20</v>
+      </c>
+      <c r="AE80" s="24"/>
+      <c r="AF80" s="24"/>
+      <c r="AG80" s="24"/>
+      <c r="AH80" s="24"/>
+      <c r="AI80" s="24"/>
+      <c r="AJ80" s="24"/>
+      <c r="AK80" s="24"/>
+      <c r="AL80" s="24"/>
+      <c r="AM80" s="24"/>
+      <c r="AN80" s="25"/>
+    </row>
+    <row r="81" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E81" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="F81" s="24"/>
       <c r="G81" s="23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H81" s="24"/>
       <c r="I81" s="24"/>
@@ -5664,185 +6412,382 @@
       <c r="L81" s="24"/>
       <c r="M81" s="24"/>
       <c r="N81" s="24"/>
-      <c r="O81" s="26"/>
-      <c r="P81" s="41">
-        <v>0.2</v>
-      </c>
-      <c r="Q81" s="41">
-        <v>0.2</v>
-      </c>
-      <c r="R81" s="41">
-        <v>0.20000000000000007</v>
-      </c>
-      <c r="S81" s="41">
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="T81" s="42">
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="U81" s="24"/>
-    </row>
-    <row r="82" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F82" s="24" t="s">
+      <c r="O81" s="43">
+        <v>0.25</v>
+      </c>
+      <c r="P81" s="43">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="Q81" s="43">
+        <v>0.8</v>
+      </c>
+      <c r="R81" s="43">
+        <v>1.45</v>
+      </c>
+      <c r="S81" s="43">
+        <v>2.5999999999999996</v>
+      </c>
+      <c r="T81" s="43">
+        <v>4.3</v>
+      </c>
+      <c r="U81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="V81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="W81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="X81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="Y81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="Z81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="AA81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="AB81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="AC81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="AD81" s="43">
+        <v>5.7</v>
+      </c>
+      <c r="AE81" s="24"/>
+      <c r="AF81" s="24"/>
+      <c r="AG81" s="24"/>
+      <c r="AH81" s="24"/>
+      <c r="AI81" s="24"/>
+      <c r="AJ81" s="24"/>
+      <c r="AK81" s="24"/>
+      <c r="AL81" s="24"/>
+      <c r="AM81" s="24"/>
+      <c r="AN81" s="25"/>
+    </row>
+    <row r="82" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E82" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="F82" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G82" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="H82" s="24"/>
+      <c r="I82" s="24"/>
+      <c r="J82" s="24"/>
+      <c r="K82" s="24"/>
+      <c r="L82" s="24"/>
+      <c r="M82" s="24"/>
+      <c r="N82" s="45">
+        <v>30290</v>
+      </c>
+      <c r="O82" s="39">
+        <v>10808</v>
+      </c>
+      <c r="P82" s="44">
+        <v>25024.6</v>
+      </c>
+      <c r="Q82" s="44">
+        <v>39241.199999999997</v>
+      </c>
+      <c r="R82" s="44">
+        <v>53457.799999999996</v>
+      </c>
+      <c r="S82" s="44">
+        <v>67674.399999999994</v>
+      </c>
+      <c r="T82" s="39">
+        <v>81891</v>
+      </c>
+      <c r="U82" s="44">
+        <v>100657.8</v>
+      </c>
+      <c r="V82" s="44">
+        <v>119424.6</v>
+      </c>
+      <c r="W82" s="44">
+        <v>138191.4</v>
+      </c>
+      <c r="X82" s="44">
+        <v>156958.19999999998</v>
+      </c>
+      <c r="Y82" s="44">
+        <v>175724.99999999997</v>
+      </c>
+      <c r="Z82" s="44">
+        <v>194491.79999999996</v>
+      </c>
+      <c r="AA82" s="44">
+        <v>213258.59999999995</v>
+      </c>
+      <c r="AB82" s="44">
+        <v>232025.39999999994</v>
+      </c>
+      <c r="AC82" s="44">
+        <v>250792.19999999992</v>
+      </c>
+      <c r="AD82" s="39">
+        <v>269559</v>
+      </c>
+      <c r="AE82" s="24"/>
+      <c r="AF82" s="24"/>
+      <c r="AG82" s="24"/>
+      <c r="AH82" s="24"/>
+      <c r="AI82" s="24"/>
+      <c r="AJ82" s="24"/>
+      <c r="AK82" s="24"/>
+      <c r="AL82" s="24"/>
+      <c r="AM82" s="24"/>
+      <c r="AN82" s="25"/>
+    </row>
+    <row r="83" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E83" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="G82" s="23" t="s">
+      <c r="F83" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="G83" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="H82" s="25"/>
-      <c r="I82" s="25">
-        <v>2423</v>
-      </c>
-      <c r="J82" s="25">
-        <v>3275</v>
-      </c>
-      <c r="K82" s="25">
-        <v>4339</v>
-      </c>
-      <c r="L82" s="25">
-        <v>8476</v>
-      </c>
-      <c r="M82" s="25">
-        <v>17600</v>
-      </c>
-      <c r="N82" s="25">
-        <v>21817</v>
-      </c>
-      <c r="O82" s="25">
-        <v>26232</v>
-      </c>
-      <c r="P82" s="28">
-        <v>27873.399999999994</v>
-      </c>
-      <c r="Q82" s="28">
-        <v>31707.100000000006</v>
-      </c>
-      <c r="R82" s="28">
-        <v>35540.799999999988</v>
-      </c>
-      <c r="S82" s="28">
-        <v>39374.5</v>
-      </c>
-      <c r="T82" s="28">
-        <v>43208.200000000012</v>
-      </c>
-      <c r="U82" s="24"/>
-    </row>
-    <row r="83" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F83" s="24" t="s">
+      <c r="H83" s="19"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="19"/>
+      <c r="K83" s="19"/>
+      <c r="L83" s="19"/>
+      <c r="M83" s="19"/>
+      <c r="N83" s="39">
+        <v>22594</v>
+      </c>
+      <c r="O83" s="39">
+        <v>31445.340470809999</v>
+      </c>
+      <c r="P83" s="39">
+        <v>53015.009948920997</v>
+      </c>
+      <c r="Q83" s="39">
+        <v>74768.033133266013</v>
+      </c>
+      <c r="R83" s="39">
+        <v>97085.80137452601</v>
+      </c>
+      <c r="S83" s="39">
+        <v>119719.602917269</v>
+      </c>
+      <c r="T83" s="39">
+        <v>142350.36580480903</v>
+      </c>
+      <c r="U83" s="39">
+        <v>165081.94181390601</v>
+      </c>
+      <c r="V83" s="39">
+        <v>187346.88963736803</v>
+      </c>
+      <c r="W83" s="39">
+        <v>210029.48462770402</v>
+      </c>
+      <c r="X83" s="39">
+        <v>232675.82927241101</v>
+      </c>
+      <c r="Y83" s="39">
+        <v>254838.99066632299</v>
+      </c>
+      <c r="Z83" s="39">
+        <v>277005.17211469699</v>
+      </c>
+      <c r="AA83" s="39">
+        <v>299162.26804125699</v>
+      </c>
+      <c r="AB83" s="39">
+        <v>321719.28957132105</v>
+      </c>
+      <c r="AC83" s="39">
+        <v>338758.85337760701</v>
+      </c>
+      <c r="AD83" s="39">
+        <v>407140.970632207</v>
+      </c>
+      <c r="AE83" s="24"/>
+      <c r="AF83" s="24"/>
+      <c r="AG83" s="24"/>
+      <c r="AH83" s="24"/>
+      <c r="AI83" s="24"/>
+      <c r="AJ83" s="24"/>
+      <c r="AK83" s="24"/>
+      <c r="AL83" s="24"/>
+      <c r="AM83" s="24"/>
+      <c r="AN83" s="25"/>
+    </row>
+    <row r="84" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E84" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="G83" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H83" s="25"/>
-      <c r="I83" s="25">
-        <v>1129</v>
-      </c>
-      <c r="J83" s="25">
-        <v>1455</v>
-      </c>
-      <c r="K83" s="25">
-        <v>1971</v>
-      </c>
-      <c r="L83" s="25">
-        <v>2272</v>
-      </c>
-      <c r="M83" s="25">
-        <v>3767</v>
-      </c>
-      <c r="N83" s="25">
-        <v>3600</v>
-      </c>
-      <c r="O83" s="25">
-        <v>4347</v>
-      </c>
-      <c r="P83" s="28">
-        <v>12526</v>
-      </c>
-      <c r="Q83" s="28">
-        <v>12526</v>
-      </c>
-      <c r="R83" s="28">
-        <v>12526</v>
-      </c>
-      <c r="S83" s="28">
-        <v>12526</v>
-      </c>
-      <c r="T83" s="28">
-        <v>12526</v>
-      </c>
-      <c r="U83" s="24"/>
-    </row>
-    <row r="84" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F84" s="24" t="s">
-        <v>97</v>
-      </c>
+      <c r="F84" s="24"/>
       <c r="G84" s="23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H84" s="24"/>
       <c r="I84" s="24"/>
       <c r="J84" s="24"/>
       <c r="K84" s="24"/>
-      <c r="L84" s="24"/>
-      <c r="M84" s="24"/>
-      <c r="N84" s="24"/>
-      <c r="O84" s="26"/>
-      <c r="P84" s="41">
-        <v>1.2800000000000001E-2</v>
-      </c>
-      <c r="Q84" s="41">
-        <v>1.2800000000000001E-2</v>
-      </c>
-      <c r="R84" s="41">
-        <v>1.2800000000000002E-2</v>
-      </c>
-      <c r="S84" s="41">
-        <v>1.2799999999999999E-2</v>
+      <c r="L84" s="42">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="M84" s="42">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="N84" s="42">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="O84" s="42">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="P84" s="42">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="Q84" s="42">
+        <v>1.4000000000000002E-3</v>
+      </c>
+      <c r="R84" s="42">
+        <v>1.5754000000000001E-2</v>
+      </c>
+      <c r="S84" s="42">
+        <v>3.0107999999999999E-2</v>
       </c>
       <c r="T84" s="42">
-        <v>1.2799999999999999E-2</v>
-      </c>
-      <c r="U84" s="24"/>
-    </row>
-    <row r="85" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F85" s="24" t="s">
-        <v>98</v>
+        <v>4.4462000000000002E-2</v>
+      </c>
+      <c r="U84" s="42">
+        <v>9.401580000000001E-2</v>
+      </c>
+      <c r="V84" s="42">
+        <v>0.14356960000000002</v>
+      </c>
+      <c r="W84" s="42">
+        <v>0.1931234</v>
+      </c>
+      <c r="X84" s="42">
+        <v>0.24267720000000001</v>
+      </c>
+      <c r="Y84" s="42">
+        <v>0.29223100000000002</v>
+      </c>
+      <c r="Z84" s="42">
+        <v>0.3417848</v>
+      </c>
+      <c r="AA84" s="42">
+        <v>0.39133860000000004</v>
+      </c>
+      <c r="AB84" s="42">
+        <v>0.44089240000000002</v>
+      </c>
+      <c r="AC84" s="42">
+        <v>0.4904462</v>
+      </c>
+      <c r="AD84" s="42">
+        <v>0.54</v>
+      </c>
+      <c r="AE84" s="24"/>
+      <c r="AF84" s="24"/>
+      <c r="AG84" s="24"/>
+      <c r="AH84" s="24"/>
+      <c r="AI84" s="24"/>
+      <c r="AJ84" s="24"/>
+      <c r="AK84" s="24"/>
+      <c r="AL84" s="24"/>
+      <c r="AM84" s="24"/>
+      <c r="AN84" s="25"/>
+    </row>
+    <row r="85" spans="5:40" x14ac:dyDescent="0.25">
+      <c r="E85" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>100</v>
       </c>
       <c r="G85" s="23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H85" s="24"/>
       <c r="I85" s="24"/>
       <c r="J85" s="24"/>
       <c r="K85" s="24"/>
-      <c r="L85" s="37"/>
-      <c r="M85" s="43">
-        <v>1.3750000000000004E-3</v>
-      </c>
-      <c r="N85" s="43">
-        <v>1.3750000000000004E-3</v>
-      </c>
-      <c r="O85" s="43">
-        <v>1.3750000000000004E-3</v>
-      </c>
-      <c r="P85" s="43">
-        <v>1.3749999999999995E-3</v>
-      </c>
-      <c r="Q85" s="43">
-        <v>0</v>
-      </c>
-      <c r="R85" s="43">
-        <v>0</v>
-      </c>
-      <c r="S85" s="43">
-        <v>0</v>
-      </c>
-      <c r="T85" s="43">
-        <v>0</v>
-      </c>
-      <c r="U85" s="24"/>
+      <c r="L85" s="42">
+        <v>3.5999999999999995E-3</v>
+      </c>
+      <c r="M85" s="42">
+        <v>3.5999999999999995E-3</v>
+      </c>
+      <c r="N85" s="42">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="O85" s="42">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="P85" s="42">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="Q85" s="42">
+        <v>5.5999999999999999E-3</v>
+      </c>
+      <c r="R85" s="42">
+        <v>6.3015999999999989E-2</v>
+      </c>
+      <c r="S85" s="42">
+        <v>0.12043199999999998</v>
+      </c>
+      <c r="T85" s="42">
+        <v>0.17784800000000001</v>
+      </c>
+      <c r="U85" s="42">
+        <v>0.37606319999999999</v>
+      </c>
+      <c r="V85" s="42">
+        <v>0.57427839999999997</v>
+      </c>
+      <c r="W85" s="42">
+        <v>0.7724936</v>
+      </c>
+      <c r="X85" s="42">
+        <v>0.97070879999999993</v>
+      </c>
+      <c r="Y85" s="42">
+        <v>1.1689240000000001</v>
+      </c>
+      <c r="Z85" s="42">
+        <v>1.3671392</v>
+      </c>
+      <c r="AA85" s="42">
+        <v>1.5653543999999999</v>
+      </c>
+      <c r="AB85" s="42">
+        <v>1.7635695999999998</v>
+      </c>
+      <c r="AC85" s="42">
+        <v>1.9617848</v>
+      </c>
+      <c r="AD85" s="42">
+        <v>2.16</v>
+      </c>
+      <c r="AE85" s="24"/>
+      <c r="AF85" s="24"/>
+      <c r="AG85" s="24"/>
+      <c r="AH85" s="24"/>
+      <c r="AI85" s="24"/>
+      <c r="AJ85" s="24"/>
+      <c r="AK85" s="24"/>
+      <c r="AL85" s="24"/>
+      <c r="AM85" s="24"/>
+      <c r="AN85" s="25"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C42:AI48">
